--- a/wr_sdm/documentation/action_descriptions.xlsx
+++ b/wr_sdm/documentation/action_descriptions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorg629193-my.sharepoint.com/personal/cpien_flowwest_com/Documents/Documents/Github/shasta-sdm/winterRunDSM/wr_sdm/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF3B62FF-A3E8-41E0-BD11-2395CAE1837E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{AF3B62FF-A3E8-41E0-BD11-2395CAE1837E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDB75354-7E9B-4B9B-BAD3-0B34BE0D392C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{08FD9470-276C-463B-A59E-530EC9C021AB}"/>
+    <workbookView minimized="1" xWindow="5430" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{08FD9470-276C-463B-A59E-530EC9C021AB}"/>
   </bookViews>
   <sheets>
     <sheet name="action_descriptions" sheetId="1" r:id="rId1"/>
@@ -752,18 +752,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -793,15 +787,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -834,10 +825,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1163,7 +1150,7 @@
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.140625" customWidth="1"/>
     <col min="4" max="4" width="44.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="44.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="44.28515625" style="3" customWidth="1"/>
     <col min="6" max="6" width="98.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1177,10 +1164,10 @@
       <c r="C1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1194,10 +1181,10 @@
       <c r="C2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1211,10 +1198,10 @@
       <c r="C3" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1228,10 +1215,10 @@
       <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1245,10 +1232,10 @@
       <c r="C5" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1262,10 +1249,10 @@
       <c r="C6" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>126</v>
       </c>
     </row>
@@ -1279,10 +1266,10 @@
       <c r="C7" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1296,10 +1283,10 @@
       <c r="C8" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1313,10 +1300,10 @@
       <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1330,10 +1317,10 @@
       <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1347,10 +1334,10 @@
       <c r="C11" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1364,10 +1351,10 @@
       <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1381,10 +1368,10 @@
       <c r="C13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1398,10 +1385,10 @@
       <c r="C14" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1415,10 +1402,10 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1432,10 +1419,10 @@
       <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1449,10 +1436,10 @@
       <c r="C17" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1466,10 +1453,10 @@
       <c r="C18" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1483,13 +1470,13 @@
       <c r="C19" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1501,10 +1488,10 @@
       <c r="C20" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1518,10 +1505,10 @@
       <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1535,10 +1522,10 @@
       <c r="C22" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1552,10 +1539,10 @@
       <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1569,10 +1556,10 @@
       <c r="C24" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1586,10 +1573,10 @@
       <c r="C25" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1603,10 +1590,10 @@
       <c r="C26" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>142</v>
       </c>
       <c r="G26" t="s">
@@ -1626,7 +1613,7 @@
       <c r="D27" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>143</v>
       </c>
     </row>
@@ -1640,10 +1627,10 @@
       <c r="C28" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>203</v>
       </c>
     </row>
@@ -1657,10 +1644,10 @@
       <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>204</v>
       </c>
     </row>
@@ -1674,10 +1661,10 @@
       <c r="C30" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>205</v>
       </c>
     </row>
@@ -1691,7 +1678,7 @@
       <c r="C31" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>201</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1708,10 +1695,10 @@
       <c r="C32" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1725,10 +1712,10 @@
       <c r="C33" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>145</v>
       </c>
     </row>
@@ -1742,10 +1729,10 @@
       <c r="C34" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1759,10 +1746,10 @@
       <c r="C35" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1779,7 +1766,7 @@
       <c r="D36" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1796,7 +1783,7 @@
       <c r="D37" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1810,10 +1797,10 @@
       <c r="C38" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="6" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1830,7 +1817,7 @@
       <c r="D39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1847,7 +1834,7 @@
       <c r="D40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1861,10 +1848,10 @@
       <c r="C41" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>202</v>
       </c>
     </row>
@@ -2042,6 +2029,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1101EA1E68817478359EA56BB205704" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bfce42929c1e9c096ec360241f2b10c8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7ab03e59-efce-49f7-b8ea-2441a68a0c86" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6f4585da6199f0af751b3359ee56b307" ns3:_="">
     <xsd:import namespace="7ab03e59-efce-49f7-b8ea-2441a68a0c86"/>
@@ -2217,22 +2219,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C9BDD57-AC21-4944-B3DB-C14C66777B9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7ab03e59-efce-49f7-b8ea-2441a68a0c86"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74580248-BAFD-455B-968D-BF9AB1740357}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC02B7BC-E49F-40C9-B856-C8E1840653BF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2248,28 +2259,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74580248-BAFD-455B-968D-BF9AB1740357}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C9BDD57-AC21-4944-B3DB-C14C66777B9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7ab03e59-efce-49f7-b8ea-2441a68a0c86"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>